--- a/SensitivityAnalysis/SingleSNP/MR_dat_gwas.xlsx
+++ b/SensitivityAnalysis/SingleSNP/MR_dat_gwas.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="72">
   <si>
     <t>SNP</t>
   </si>
@@ -233,16 +233,7 @@
     <t xml:space="preserve">Non-cancer illness code, self-reported: hypertension ||  || </t>
   </si>
   <si>
-    <t>ebi-a-GCST006867</t>
-  </si>
-  <si>
-    <t>Type 2 diabetes || id:ebi-a-GCST006867</t>
-  </si>
-  <si>
-    <t>Type 2 diabetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type 2 diabetes ||  || </t>
+    <t>T2DM</t>
   </si>
 </sst>
 </file>
@@ -433,7 +424,7 @@
         <v>43</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H2" t="n">
         <v>-0.0389008</v>
@@ -679,7 +670,7 @@
         <v>43</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H2" t="n">
         <v>0.0706</v>
@@ -925,7 +916,7 @@
         <v>43</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H2" t="n">
         <v>-0.0115</v>
@@ -1183,7 +1174,7 @@
         <v>43</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H2" t="n">
         <v>-0.010354</v>
@@ -1423,7 +1414,7 @@
         <v>43</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H2" t="n">
         <v>-0.0117</v>
@@ -1663,7 +1654,7 @@
         <v>43</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H2" t="n">
         <v>-5.73167E-4</v>
@@ -1820,85 +1811,67 @@
         <v>12</v>
       </c>
       <c r="O1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="R1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T1" t="s">
+        <v>25</v>
+      </c>
+      <c r="U1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" t="s">
+        <v>28</v>
+      </c>
+      <c r="X1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI1" t="s">
         <v>16</v>
-      </c>
-      <c r="S1" t="s">
-        <v>17</v>
-      </c>
-      <c r="T1" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" t="s">
-        <v>19</v>
-      </c>
-      <c r="V1" t="s">
-        <v>20</v>
-      </c>
-      <c r="W1" t="s">
-        <v>21</v>
-      </c>
-      <c r="X1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="2">
@@ -1921,16 +1894,16 @@
         <v>43</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0109</v>
+        <v>-0.0187</v>
       </c>
       <c r="I2" t="n">
         <v>0.6699</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6135740000000001</v>
+        <v>0.6063</v>
       </c>
       <c r="K2" t="s">
         <v>44</v>
@@ -1944,86 +1917,68 @@
       <c r="N2" t="s">
         <v>71</v>
       </c>
-      <c r="O2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P2" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.008</v>
+      <c r="O2" t="n">
+        <v>0.0066</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.004583</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>71</v>
       </c>
       <c r="R2" t="n">
-        <v>62892.0</v>
+        <v>1.0</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1725</v>
-      </c>
-      <c r="T2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U2" t="s">
-        <v>73</v>
-      </c>
-      <c r="V2" t="s">
-        <v>74</v>
-      </c>
-      <c r="W2" t="s">
+        <v>0.028311</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.055134</v>
+      </c>
+      <c r="U2" t="n">
+        <v>6.097554</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.11E-9</v>
+      </c>
+      <c r="W2" t="n">
+        <v>8.955015</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5.563072</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.061943</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.640486</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>49372.0</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.00684234693877551</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="AH2" t="s">
         <v>51</v>
       </c>
-      <c r="X2" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0.028311</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.055134</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>6.097554</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.11E-9</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>8.955015</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>5.563072</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0.061943</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0.640486</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>49372.0</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>53</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0.00684234693877551</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>54</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>54</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>51</v>
+      <c r="AI2" t="e">
+        <v>#N/A</v>
       </c>
     </row>
   </sheetData>
